--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_override_labor_grid" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="453">
   <si>
     <t>TC ID</t>
   </si>
@@ -1420,7 +1421,10 @@
     <t>Pass:48 Fail:0 Skipped:0 Blocked:0</t>
   </si>
   <si>
-    <t>Last Updated: 2026-08-13</t>
+    <t>Last Updated: 2026-07-31</t>
+  </si>
+  <si>
+    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
   </si>
 </sst>
 </file>
@@ -10520,4 +10524,20 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>18ff78cd3fbd5f1eaea8671aab16ad4934208919e92d0cf838fb3049b31c1e53</t>
+    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>6729770ff2e77acf7dfad5e1019f025e9612e9fa3d5a8ea5b9a5f4adb8ffb470</t>
+    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>216e3ef472e1d1a5fd8bdc823b2299e2983f8e64bb024549c10be824c756f7bc</t>
+    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>f9d696e3767564ce556785ab32c8d4d620422045a781f574890b1a82aec41d64</t>
+    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>57a96ebc2a9427589cbb7cc0296e9f637c842c12b7f8c8e0ccb6cf435e12d27f</t>
+    <t>e654a4f812c4ac1bbbd49bec0a6a66cc601c73fe4374e6e441effe43a9071f32</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>277fceb9bb3698d9453fc43411968cd91d3f9449455906d5d23de81a08ec2170</t>
+    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>380d8e0d585bd783101a2b952772f0a3767a293b55ceefd229d969fdbd06bb46</t>
+    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>cac2701a5bdd1841a1d0e7e6b5d664c8adc61c2fa348a93419b1f3051fe19823</t>
+    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>f28c807cfb6eeb8b94ac190190f1358c8dc4f8c37d5142ffe46b461a0507db07</t>
+    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>d96ccb59875274442c18342f06a9aa9c3097f6ed8a4e1cb1fd5e32267acbe42c</t>
+    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>49b6bbaa1b0534e99f83598cc30c0c62ecee0b835796d356c2fde35f8e610e29</t>
+    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>a5f7d6500d58722995e66601ec026824ea3e350a07badce9343a7a492d496f36</t>
+    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -1424,7 +1424,7 @@
     <t>Last Updated: 2026-07-31</t>
   </si>
   <si>
-    <t>636a977849267dc2016113abf29c1c780ee08ec327c6f8ab32a1e036b3a6cf92</t>
+    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>

--- a/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
+++ b/clients/encore/testcases/corporate-override/corporate-override-labor-grid.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="corporate_override_labor_grid" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="__fp__" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="452">
   <si>
     <t>TC ID</t>
   </si>
@@ -1422,9 +1421,6 @@
   </si>
   <si>
     <t>Last Updated: 2026-07-31</t>
-  </si>
-  <si>
-    <t>9b801757218047b86420f352cec3e581306b4bdd9151437dfc89dac28f323abc</t>
   </si>
 </sst>
 </file>
@@ -10524,20 +10520,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>452</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>